--- a/Data/EC/NIT-9018865871.xlsx
+++ b/Data/EC/NIT-9018865871.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18CFADDF-4C92-4A1A-8923-605C43CBFB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FA9DF78-5B17-4B5F-9640-9661BDDF1E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{0015DB0C-4C39-42F8-AA92-ED9C061651F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CDBE5D0B-362D-4935-89C0-7B2B23909E1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -650,22 +650,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD0AB50B-9800-CDA7-4F4D-FF71FCC54BFD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30F4BBCC-7FA3-32C8-6789-04C817E2C9C9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -674,7 +674,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -687,7 +687,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1016,23 +1016,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9074BF8-DEBC-45BD-928B-7ABD37E63381}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84F55EF-243C-4BD0-A6AE-D764C612C01F}">
   <dimension ref="B2:J181"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1045,7 +1045,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1056,7 +1056,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1067,7 +1067,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1078,8 +1078,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>72</v>
       </c>
@@ -1094,8 +1094,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1110,8 +1110,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>73</v>
       </c>
@@ -1126,8 +1126,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>74</v>
       </c>
@@ -1146,7 +1146,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1198,7 +1198,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1221,7 +1221,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1244,7 +1244,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1267,7 +1267,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1290,7 +1290,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1313,7 +1313,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1336,7 +1336,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1359,7 +1359,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1382,7 +1382,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1405,7 +1405,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1428,7 +1428,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1451,7 +1451,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1474,7 +1474,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1497,7 +1497,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1543,7 +1543,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1566,7 +1566,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1589,7 +1589,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1612,7 +1612,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1658,7 +1658,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1681,7 +1681,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1704,7 +1704,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1727,7 +1727,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1750,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1773,7 +1773,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1796,7 +1796,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1819,7 +1819,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1842,7 +1842,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1865,7 +1865,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1888,7 +1888,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1911,7 +1911,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1934,7 +1934,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1957,7 +1957,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1980,7 +1980,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2003,7 +2003,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2026,7 +2026,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2049,7 +2049,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2072,7 +2072,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2095,7 +2095,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2118,7 +2118,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2141,7 +2141,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2164,7 +2164,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2187,7 +2187,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2210,7 +2210,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2233,7 +2233,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2279,7 +2279,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2302,7 +2302,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2325,7 +2325,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2348,7 +2348,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2371,7 +2371,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2394,7 +2394,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2417,7 +2417,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2440,7 +2440,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2463,7 +2463,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2486,7 +2486,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2509,7 +2509,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2532,7 +2532,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2555,7 +2555,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2578,7 +2578,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2601,7 +2601,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2647,7 +2647,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2670,7 +2670,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2693,7 +2693,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2716,7 +2716,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2739,7 +2739,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2762,7 +2762,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2785,7 +2785,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2808,7 +2808,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2831,7 +2831,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2854,7 +2854,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2877,7 +2877,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2900,7 +2900,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2923,7 +2923,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2946,7 +2946,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -2969,7 +2969,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -2992,7 +2992,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3015,7 +3015,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3038,7 +3038,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3061,7 +3061,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3084,7 +3084,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3107,7 +3107,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3130,7 +3130,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3153,7 +3153,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3176,7 +3176,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3199,7 +3199,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3222,7 +3222,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3245,7 +3245,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3268,7 +3268,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3291,7 +3291,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3314,7 +3314,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3337,7 +3337,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3360,7 +3360,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3383,7 +3383,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3406,7 +3406,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3429,7 +3429,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3452,7 +3452,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3475,7 +3475,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3498,7 +3498,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3521,7 +3521,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3544,7 +3544,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3567,7 +3567,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3590,7 +3590,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3613,7 +3613,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3636,7 +3636,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3659,7 +3659,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3682,7 +3682,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3705,7 +3705,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3728,7 +3728,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3751,7 +3751,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3774,7 +3774,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3797,7 +3797,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3820,7 +3820,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3843,7 +3843,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3866,7 +3866,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3889,7 +3889,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -3912,7 +3912,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -3935,7 +3935,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -3958,7 +3958,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -3981,7 +3981,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -4004,7 +4004,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4027,7 +4027,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4050,7 +4050,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4073,7 +4073,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4096,7 +4096,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4119,7 +4119,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4142,7 +4142,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4165,7 +4165,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4188,7 +4188,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4211,7 +4211,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4234,7 +4234,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4257,7 +4257,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4280,7 +4280,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4303,7 +4303,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4326,7 +4326,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4349,7 +4349,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
@@ -4372,7 +4372,7 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
@@ -4418,7 +4418,7 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
@@ -4441,7 +4441,7 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>64</v>
       </c>
@@ -4464,7 +4464,7 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>64</v>
       </c>
@@ -4487,7 +4487,7 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>64</v>
       </c>
@@ -4510,7 +4510,7 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>64</v>
       </c>
@@ -4533,7 +4533,7 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>64</v>
       </c>
@@ -4556,7 +4556,7 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>64</v>
       </c>
@@ -4579,7 +4579,7 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>64</v>
       </c>
@@ -4602,7 +4602,7 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>64</v>
       </c>
@@ -4625,7 +4625,7 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>64</v>
       </c>
@@ -4648,7 +4648,7 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>64</v>
       </c>
@@ -4671,7 +4671,7 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>64</v>
       </c>
@@ -4694,7 +4694,7 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>64</v>
       </c>
@@ -4717,7 +4717,7 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
@@ -4740,7 +4740,7 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
@@ -4763,7 +4763,7 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
@@ -4786,7 +4786,7 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
@@ -4809,7 +4809,7 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
@@ -4832,7 +4832,7 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="21" t="s">
         <v>8</v>
       </c>
@@ -4855,7 +4855,7 @@
       <c r="I175" s="25"/>
       <c r="J175" s="26"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="32" t="s">
         <v>80</v>
       </c>
@@ -4866,7 +4866,7 @@
       <c r="I180" s="1"/>
       <c r="J180" s="1"/>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="32" t="s">
         <v>79</v>
       </c>
